--- a/final_data_pipeline/output/311513longform.xlsx
+++ b/final_data_pipeline/output/311513longform.xlsx
@@ -1781,7 +1781,7 @@
         <v>101</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1870,7 +1870,7 @@
         <v>101</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1962,7 +1962,7 @@
         <v>101</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -2057,7 +2057,7 @@
         <v>101</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2146,7 +2146,7 @@
         <v>101</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2235,7 +2235,7 @@
         <v>101</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2324,7 +2324,7 @@
         <v>101</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2413,7 +2413,7 @@
         <v>101</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2502,7 +2502,7 @@
         <v>101</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2594,7 +2594,7 @@
         <v>101</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2689,7 +2689,7 @@
         <v>101</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2778,7 +2778,7 @@
         <v>101</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2867,7 +2867,7 @@
         <v>101</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2956,7 +2956,7 @@
         <v>101</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -3045,7 +3045,7 @@
         <v>101</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -3134,7 +3134,7 @@
         <v>101</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB27">
         <v>8000</v>
@@ -3226,7 +3226,7 @@
         <v>101</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB28">
         <v>8000</v>
@@ -3324,7 +3324,7 @@
         <v>101</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB29">
         <v>8000</v>
@@ -3422,7 +3422,7 @@
         <v>101</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB30">
         <v>8000</v>
@@ -3520,7 +3520,7 @@
         <v>101</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB31">
         <v>8000</v>
@@ -3612,7 +3612,7 @@
         <v>101</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3710,7 +3710,7 @@
         <v>101</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3799,7 +3799,7 @@
         <v>101</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -3888,7 +3888,7 @@
         <v>101</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -3977,7 +3977,7 @@
         <v>101</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB36">
         <v>8000</v>
@@ -4066,7 +4066,7 @@
         <v>101</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -4155,7 +4155,7 @@
         <v>101</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -4244,7 +4244,7 @@
         <v>101</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4333,7 +4333,7 @@
         <v>101</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4422,7 +4422,7 @@
         <v>101</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4511,7 +4511,7 @@
         <v>101</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4600,7 +4600,7 @@
         <v>101</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4689,7 +4689,7 @@
         <v>101</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4778,7 +4778,7 @@
         <v>101</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4867,7 +4867,7 @@
         <v>101</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -4956,7 +4956,7 @@
         <v>101</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -5045,7 +5045,7 @@
         <v>101</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -5134,7 +5134,7 @@
         <v>101</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -5226,7 +5226,7 @@
         <v>101</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5315,7 +5315,7 @@
         <v>101</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5407,7 +5407,7 @@
         <v>101</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5502,7 +5502,7 @@
         <v>101</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5591,7 +5591,7 @@
         <v>101</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5680,7 +5680,7 @@
         <v>101</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5769,7 +5769,7 @@
         <v>101</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5858,7 +5858,7 @@
         <v>101</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5947,7 +5947,7 @@
         <v>101</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -6036,7 +6036,7 @@
         <v>101</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6125,7 +6125,7 @@
         <v>101</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6214,7 +6214,7 @@
         <v>101</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6303,7 +6303,7 @@
         <v>101</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6392,7 +6392,7 @@
         <v>101</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6481,7 +6481,7 @@
         <v>101</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6570,7 +6570,7 @@
         <v>101</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6662,7 +6662,7 @@
         <v>101</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6754,7 +6754,7 @@
         <v>101</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -6849,7 +6849,7 @@
         <v>101</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -6938,7 +6938,7 @@
         <v>101</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -7027,7 +7027,7 @@
         <v>101</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -7116,7 +7116,7 @@
         <v>101</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7659,7 +7659,7 @@
         <v>101</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -7748,7 +7748,7 @@
         <v>101</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -7840,7 +7840,7 @@
         <v>101</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -7935,7 +7935,7 @@
         <v>101</v>
       </c>
       <c r="AA80">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB80">
         <v>8000</v>
@@ -8024,7 +8024,7 @@
         <v>101</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -11030,7 +11030,7 @@
         <v>101</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -11125,7 +11125,7 @@
         <v>101</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -11214,7 +11214,7 @@
         <v>101</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11303,7 +11303,7 @@
         <v>101</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11392,7 +11392,7 @@
         <v>101</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -11481,7 +11481,7 @@
         <v>101</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11570,7 +11570,7 @@
         <v>101</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11659,7 +11659,7 @@
         <v>101</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -11748,7 +11748,7 @@
         <v>101</v>
       </c>
       <c r="AA122">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB122">
         <v>8000</v>
@@ -11837,7 +11837,7 @@
         <v>101</v>
       </c>
       <c r="AA123">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB123">
         <v>8000</v>
@@ -11926,7 +11926,7 @@
         <v>101</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -12015,7 +12015,7 @@
         <v>101</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -12107,7 +12107,7 @@
         <v>101</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -12199,7 +12199,7 @@
         <v>101</v>
       </c>
       <c r="AA127">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB127">
         <v>8000</v>
@@ -12294,7 +12294,7 @@
         <v>101</v>
       </c>
       <c r="AA128">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB128">
         <v>8000</v>
@@ -12383,7 +12383,7 @@
         <v>101</v>
       </c>
       <c r="AA129">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB129">
         <v>8000</v>
@@ -12472,7 +12472,7 @@
         <v>101</v>
       </c>
       <c r="AA130">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB130">
         <v>8000</v>
@@ -12564,7 +12564,7 @@
         <v>101</v>
       </c>
       <c r="AA131">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB131">
         <v>8000</v>
@@ -12659,7 +12659,7 @@
         <v>101</v>
       </c>
       <c r="AA132">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB132">
         <v>8000</v>
@@ -12748,7 +12748,7 @@
         <v>101</v>
       </c>
       <c r="AA133">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB133">
         <v>8000</v>
@@ -12837,7 +12837,7 @@
         <v>101</v>
       </c>
       <c r="AA134">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB134">
         <v>8000</v>
@@ -12926,7 +12926,7 @@
         <v>101</v>
       </c>
       <c r="AA135">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB135">
         <v>8000</v>
@@ -13015,7 +13015,7 @@
         <v>101</v>
       </c>
       <c r="AA136">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB136">
         <v>8000</v>
@@ -13104,7 +13104,7 @@
         <v>101</v>
       </c>
       <c r="AA137">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB137">
         <v>8000</v>
@@ -13196,7 +13196,7 @@
         <v>101</v>
       </c>
       <c r="AA138">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB138">
         <v>8000</v>
@@ -13294,7 +13294,7 @@
         <v>101</v>
       </c>
       <c r="AA139">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB139">
         <v>8000</v>
@@ -13389,7 +13389,7 @@
         <v>101</v>
       </c>
       <c r="AA140">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB140">
         <v>8000</v>
@@ -13481,7 +13481,7 @@
         <v>101</v>
       </c>
       <c r="AA141">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB141">
         <v>8000</v>
@@ -13579,7 +13579,7 @@
         <v>101</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -13674,7 +13674,7 @@
         <v>101</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -13763,7 +13763,7 @@
         <v>101</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -13852,7 +13852,7 @@
         <v>101</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>101</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -14033,7 +14033,7 @@
         <v>101</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -14131,7 +14131,7 @@
         <v>101</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -14226,7 +14226,7 @@
         <v>101</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -14315,7 +14315,7 @@
         <v>101</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -14404,7 +14404,7 @@
         <v>101</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -14493,7 +14493,7 @@
         <v>101</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -14582,7 +14582,7 @@
         <v>101</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -14671,7 +14671,7 @@
         <v>101</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB154">
         <v>8000</v>
@@ -14760,7 +14760,7 @@
         <v>101</v>
       </c>
       <c r="AA155">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB155">
         <v>8000</v>
@@ -14849,7 +14849,7 @@
         <v>101</v>
       </c>
       <c r="AA156">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB156">
         <v>8000</v>
@@ -14938,7 +14938,7 @@
         <v>101</v>
       </c>
       <c r="AA157">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB157">
         <v>8000</v>
@@ -15027,7 +15027,7 @@
         <v>101</v>
       </c>
       <c r="AA158">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB158">
         <v>8000</v>
@@ -15116,7 +15116,7 @@
         <v>101</v>
       </c>
       <c r="AA159">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB159">
         <v>8000</v>
@@ -15205,7 +15205,7 @@
         <v>101</v>
       </c>
       <c r="AA160">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB160">
         <v>8000</v>
@@ -15294,7 +15294,7 @@
         <v>101</v>
       </c>
       <c r="AA161">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB161">
         <v>8000</v>
@@ -15383,7 +15383,7 @@
         <v>101</v>
       </c>
       <c r="AA162">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB162">
         <v>8000</v>
@@ -15472,7 +15472,7 @@
         <v>101</v>
       </c>
       <c r="AA163">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB163">
         <v>8000</v>
@@ -15561,7 +15561,7 @@
         <v>101</v>
       </c>
       <c r="AA164">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB164">
         <v>8000</v>
@@ -15653,7 +15653,7 @@
         <v>101</v>
       </c>
       <c r="AA165">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB165">
         <v>8000</v>
@@ -15748,7 +15748,7 @@
         <v>101</v>
       </c>
       <c r="AA166">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB166">
         <v>8000</v>
@@ -15837,7 +15837,7 @@
         <v>101</v>
       </c>
       <c r="AA167">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB167">
         <v>8000</v>
@@ -15926,7 +15926,7 @@
         <v>101</v>
       </c>
       <c r="AA168">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB168">
         <v>8000</v>
@@ -16018,7 +16018,7 @@
         <v>101</v>
       </c>
       <c r="AA169">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB169">
         <v>8000</v>
@@ -16107,7 +16107,7 @@
         <v>101</v>
       </c>
       <c r="AA170">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB170">
         <v>8000</v>
@@ -16196,7 +16196,7 @@
         <v>101</v>
       </c>
       <c r="AA171">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB171">
         <v>8000</v>
@@ -16285,7 +16285,7 @@
         <v>101</v>
       </c>
       <c r="AA172">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB172">
         <v>8000</v>
@@ -16374,7 +16374,7 @@
         <v>101</v>
       </c>
       <c r="AA173">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB173">
         <v>8000</v>
